--- a/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/Сыр проблема/СЫРЫ в Крым.xlsx
+++ b/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/Сыр проблема/СЫРЫ в Крым.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\ПРОБЛЕМЫ\Сыр проблема\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\ПРОБЛЕМЫ\Сыр проблема\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CADD32E-6238-4F80-BBB4-DE2F4133F83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DED7903-012F-48FB-A79D-EC9A8EB1E5D2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -87,7 +87,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -95,12 +95,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -385,6 +401,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -393,68 +410,68 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>100</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>100</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>40</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>100</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>180</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -464,50 +481,51 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>120</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>220</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>30</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>50</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/Сыр проблема/СЫРЫ в Крым.xlsx
+++ b/РАБОЧИЙ СТОЛ/ПРОБЛЕМЫ/Сыр проблема/СЫРЫ в Крым.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\ПРОБЛЕМЫ\Сыр проблема\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DED7903-012F-48FB-A79D-EC9A8EB1E5D2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDB5221-38C7-41E6-9622-1280EC10ECD6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>из Бердянска</t>
   </si>
@@ -64,19 +64,56 @@
   </si>
   <si>
     <t>Сыч/Прод Коровино Российский Оригин 50% ВЕС НОВАЯ (3,5 кг)  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>до 08.12</t>
+  </si>
+  <si>
+    <t>до 27.11</t>
+  </si>
+  <si>
+    <t>до 25.09</t>
+  </si>
+  <si>
+    <t>до 29.08</t>
+  </si>
+  <si>
+    <t>Сыч/Прод Коровино Тильзитер Оригин 50% ВЕС (3,5 кг брус) СЗМЖ  Останкино</t>
+  </si>
+  <si>
+    <t>до 27.08</t>
+  </si>
+  <si>
+    <t>до 12.09</t>
+  </si>
+  <si>
+    <t>до 07.10</t>
+  </si>
+  <si>
+    <t>до 15.11</t>
+  </si>
+  <si>
+    <t>до 14.10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2C2D2E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -114,9 +151,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -397,19 +436,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -419,8 +459,11 @@
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -430,8 +473,11 @@
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -441,8 +487,11 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -452,8 +501,11 @@
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -463,8 +515,11 @@
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -474,13 +529,16 @@
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -490,8 +548,11 @@
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -501,8 +562,11 @@
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -512,8 +576,11 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -522,6 +589,23 @@
       </c>
       <c r="C13" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1">
+        <v>100</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
